--- a/demo/pq-sales.xlsx
+++ b/demo/pq-sales.xlsx
@@ -125,5 +125,5 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<DataMashup xmlns="http://schemas.microsoft.com/DataMashup">AAAAAKgDAABQSwMEFAAAAAgAOJn1XH+/08qcAAAA5AAAABMAAABbQ29udGVudF9UeXBlc10ueG1sbY5LDsIwDESvEnmfurBACDXtArgBF4iC+xHNR42Lwu1J6A516Zl5nmm6ZGfxpiVO3ik4VDUIcsY/JzcoWLmXZ+ja5vEJFEWOuqhgZA4XxGhGsjpWPpDLTu8Xqzmfy4BBm5ceCI91fULjHZNjyeUHtM2Ner3OLO4py1ttxkFct1ypUsCUGIuMu4D9i+sQ5sloziYmaaO0BcTf7PYLUEsDBBQAAAAIADiZ9Vy5xFaLhwAAALsAAAASAAAAQ29uZmlnL1BhY2thZ2UueG1sTY3BCgIhFEV/RdyPb2oV8XQWtR0IovZiziiNOugz+vwGSmh3D9x7Dw7vsLCXzcWnKPlO9JzZaNLDx1nySlN34IPCizZPPVu2lWOR3BGtR4BinA26iOBNTiVNJEwKcNakR11cXeE34wrvX4Paix6hAY4+tryZEf4YT3Whmq2ysbtdERpiO1UfUEsDBBQAAAAIADiZ9VwltBmRGwEAAAMCAAATAAAARm9ybXVsYXMvU2VjdGlvbjEubV2QPWvDMBCGd/+Kw5NTTCBDp5BCCe3YNrEhg/Gg2FcsIktBOrUNxv+958+YeLF00j3vc3JYkDQakuG/2QaBq4TFEj49XT3BDhRSAPwlxtsCufD2V6Ba7721qOlk7OVszCVaNdmHqHEXJkKhC/M22xtNfCOP+/b0dmXqDlJxVrhOrdDu29h6b5SvdXfooiEhhqYJD3QLYyAug/b1GW3L5fDLygIf6u1q4L9LRdiJTxEJKh7qaH5d1GfHgKKoIGN0Di/wPPYdUbP2vW3YD1oumqgLqfDghSbJ6zn7JKlKDQk1U17LckBEI5/7+hsMGDVGSg5PkPWD5SMtUbJe6NTmZ9aZg+6vMTkkxtJyet5GHak3n6I3rBxIvWjYBv9QSwECFAAUAAAACAA4mfVcf7/TypwAAADkAAAAEwAAAAAAAAAAAAAAAAAAAAAAW0NvbnRlbnRfVHlwZXNdLnhtbFBLAQIUABQAAAAIADiZ9Vy5xFaLhwAAALsAAAASAAAAAAAAAAAAAAAAAM0AAABDb25maWcvUGFja2FnZS54bWxQSwECFAAUAAAACAA4mfVcJbQZkRsBAAADAgAAEwAAAAAAAAAAAAAAAACEAQAARm9ybXVsYXMvU2VjdGlvbjEubVBLBQYAAAAAAwADAMIAAADQAgAAAADXAAAAPD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXRmLTgiPz48UGVybWlzc2lvbkxpc3QgeG1sbnM6eHNkPSJodHRwOi8vd3d3LnczLm9yZy8yMDAxL1hNTFNjaGVtYSI+PENhbkV2YWx1YXRlRnV0dXJlUGFja2FnZXM+ZmFsc2U8L0NhbkV2YWx1YXRlRnV0dXJlUGFja2FnZXM+PEZpcmV3YWxsRW5hYmxlZD50cnVlPC9GaXJld2FsbEVuYWJsZWQ+PC9QZXJtaXNzaW9uTGlzdD4AAAAAAAAAAA==</DataMashup>
+<DataMashup xmlns="http://schemas.microsoft.com/DataMashup">AAAAAKgDAABQSwMEFAAAAAgAa7r1XH+/08qcAAAA5AAAABMAAABbQ29udGVudF9UeXBlc10ueG1sbY5LDsIwDESvEnmfurBACDXtArgBF4iC+xHNR42Lwu1J6A516Zl5nmm6ZGfxpiVO3ik4VDUIcsY/JzcoWLmXZ+ja5vEJFEWOuqhgZA4XxGhGsjpWPpDLTu8Xqzmfy4BBm5ceCI91fULjHZNjyeUHtM2Ner3OLO4py1ttxkFct1ypUsCUGIuMu4D9i+sQ5sloziYmaaO0BcTf7PYLUEsDBBQAAAAIAGu69Vy5xFaLhwAAALsAAAASAAAAQ29uZmlnL1BhY2thZ2UueG1sTY3BCgIhFEV/RdyPb2oV8XQWtR0IovZiziiNOugz+vwGSmh3D9x7Dw7vsLCXzcWnKPlO9JzZaNLDx1nySlN34IPCizZPPVu2lWOR3BGtR4BinA26iOBNTiVNJEwKcNakR11cXeE34wrvX4Paix6hAY4+tryZEf4YT3Whmq2ysbtdERpiO1UfUEsDBBQAAAAIAGu69VwltBmRGwEAAAMCAAATAAAARm9ybXVsYXMvU2VjdGlvbjEubV2QPWvDMBCGd/+Kw5NTTCBDp5BCCe3YNrEhg/Gg2FcsIktBOrUNxv+958+YeLF00j3vc3JYkDQakuG/2QaBq4TFEj49XT3BDhRSAPwlxtsCufD2V6Ba7721qOlk7OVszCVaNdmHqHEXJkKhC/M22xtNfCOP+/b0dmXqDlJxVrhOrdDu29h6b5SvdXfooiEhhqYJD3QLYyAug/b1GW3L5fDLygIf6u1q4L9LRdiJTxEJKh7qaH5d1GfHgKKoIGN0Di/wPPYdUbP2vW3YD1oumqgLqfDghSbJ6zn7JKlKDQk1U17LckBEI5/7+hsMGDVGSg5PkPWD5SMtUbJe6NTmZ9aZg+6vMTkkxtJyet5GHak3n6I3rBxIvWjYBv9QSwECFAAUAAAACABruvVcf7/TypwAAADkAAAAEwAAAAAAAAAAAAAAAAAAAAAAW0NvbnRlbnRfVHlwZXNdLnhtbFBLAQIUABQAAAAIAGu69Vy5xFaLhwAAALsAAAASAAAAAAAAAAAAAAAAAM0AAABDb25maWcvUGFja2FnZS54bWxQSwECFAAUAAAACABruvVcJbQZkRsBAAADAgAAEwAAAAAAAAAAAAAAAACEAQAARm9ybXVsYXMvU2VjdGlvbjEubVBLBQYAAAAAAwADAMIAAADQAgAAAADXAAAAPD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXRmLTgiPz48UGVybWlzc2lvbkxpc3QgeG1sbnM6eHNkPSJodHRwOi8vd3d3LnczLm9yZy8yMDAxL1hNTFNjaGVtYSI+PENhbkV2YWx1YXRlRnV0dXJlUGFja2FnZXM+ZmFsc2U8L0NhbkV2YWx1YXRlRnV0dXJlUGFja2FnZXM+PEZpcmV3YWxsRW5hYmxlZD50cnVlPC9GaXJld2FsbEVuYWJsZWQ+PC9QZXJtaXNzaW9uTGlzdD4AAAAAAAAAAA==</DataMashup>
 </file>
--- a/demo/pq-sales.xlsx
+++ b/demo/pq-sales.xlsx
@@ -125,5 +125,5 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<DataMashup xmlns="http://schemas.microsoft.com/DataMashup">AAAAAKgDAABQSwMEFAAAAAgAa7r1XH+/08qcAAAA5AAAABMAAABbQ29udGVudF9UeXBlc10ueG1sbY5LDsIwDESvEnmfurBACDXtArgBF4iC+xHNR42Lwu1J6A516Zl5nmm6ZGfxpiVO3ik4VDUIcsY/JzcoWLmXZ+ja5vEJFEWOuqhgZA4XxGhGsjpWPpDLTu8Xqzmfy4BBm5ceCI91fULjHZNjyeUHtM2Ner3OLO4py1ttxkFct1ypUsCUGIuMu4D9i+sQ5sloziYmaaO0BcTf7PYLUEsDBBQAAAAIAGu69Vy5xFaLhwAAALsAAAASAAAAQ29uZmlnL1BhY2thZ2UueG1sTY3BCgIhFEV/RdyPb2oV8XQWtR0IovZiziiNOugz+vwGSmh3D9x7Dw7vsLCXzcWnKPlO9JzZaNLDx1nySlN34IPCizZPPVu2lWOR3BGtR4BinA26iOBNTiVNJEwKcNakR11cXeE34wrvX4Paix6hAY4+tryZEf4YT3Whmq2ysbtdERpiO1UfUEsDBBQAAAAIAGu69VwltBmRGwEAAAMCAAATAAAARm9ybXVsYXMvU2VjdGlvbjEubV2QPWvDMBCGd/+Kw5NTTCBDp5BCCe3YNrEhg/Gg2FcsIktBOrUNxv+958+YeLF00j3vc3JYkDQakuG/2QaBq4TFEj49XT3BDhRSAPwlxtsCufD2V6Ba7721qOlk7OVszCVaNdmHqHEXJkKhC/M22xtNfCOP+/b0dmXqDlJxVrhOrdDu29h6b5SvdXfooiEhhqYJD3QLYyAug/b1GW3L5fDLygIf6u1q4L9LRdiJTxEJKh7qaH5d1GfHgKKoIGN0Di/wPPYdUbP2vW3YD1oumqgLqfDghSbJ6zn7JKlKDQk1U17LckBEI5/7+hsMGDVGSg5PkPWD5SMtUbJe6NTmZ9aZg+6vMTkkxtJyet5GHak3n6I3rBxIvWjYBv9QSwECFAAUAAAACABruvVcf7/TypwAAADkAAAAEwAAAAAAAAAAAAAAAAAAAAAAW0NvbnRlbnRfVHlwZXNdLnhtbFBLAQIUABQAAAAIAGu69Vy5xFaLhwAAALsAAAASAAAAAAAAAAAAAAAAAM0AAABDb25maWcvUGFja2FnZS54bWxQSwECFAAUAAAACABruvVcJbQZkRsBAAADAgAAEwAAAAAAAAAAAAAAAACEAQAARm9ybXVsYXMvU2VjdGlvbjEubVBLBQYAAAAAAwADAMIAAADQAgAAAADXAAAAPD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXRmLTgiPz48UGVybWlzc2lvbkxpc3QgeG1sbnM6eHNkPSJodHRwOi8vd3d3LnczLm9yZy8yMDAxL1hNTFNjaGVtYSI+PENhbkV2YWx1YXRlRnV0dXJlUGFja2FnZXM+ZmFsc2U8L0NhbkV2YWx1YXRlRnV0dXJlUGFja2FnZXM+PEZpcmV3YWxsRW5hYmxlZD50cnVlPC9GaXJld2FsbEVuYWJsZWQ+PC9QZXJtaXNzaW9uTGlzdD4AAAAAAAAAAA==</DataMashup>
+<DataMashup xmlns="http://schemas.microsoft.com/DataMashup">AAAAAKgDAABQSwMEFAAAAAgAwr71XH+/08qcAAAA5AAAABMAAABbQ29udGVudF9UeXBlc10ueG1sbY5LDsIwDESvEnmfurBACDXtArgBF4iC+xHNR42Lwu1J6A516Zl5nmm6ZGfxpiVO3ik4VDUIcsY/JzcoWLmXZ+ja5vEJFEWOuqhgZA4XxGhGsjpWPpDLTu8Xqzmfy4BBm5ceCI91fULjHZNjyeUHtM2Ner3OLO4py1ttxkFct1ypUsCUGIuMu4D9i+sQ5sloziYmaaO0BcTf7PYLUEsDBBQAAAAIAMK+9Vy5xFaLhwAAALsAAAASAAAAQ29uZmlnL1BhY2thZ2UueG1sTY3BCgIhFEV/RdyPb2oV8XQWtR0IovZiziiNOugz+vwGSmh3D9x7Dw7vsLCXzcWnKPlO9JzZaNLDx1nySlN34IPCizZPPVu2lWOR3BGtR4BinA26iOBNTiVNJEwKcNakR11cXeE34wrvX4Paix6hAY4+tryZEf4YT3Whmq2ysbtdERpiO1UfUEsDBBQAAAAIAMK+9VwltBmRGwEAAAMCAAATAAAARm9ybXVsYXMvU2VjdGlvbjEubV2QPWvDMBCGd/+Kw5NTTCBDp5BCCe3YNrEhg/Gg2FcsIktBOrUNxv+958+YeLF00j3vc3JYkDQakuG/2QaBq4TFEj49XT3BDhRSAPwlxtsCufD2V6Ba7721qOlk7OVszCVaNdmHqHEXJkKhC/M22xtNfCOP+/b0dmXqDlJxVrhOrdDu29h6b5SvdXfooiEhhqYJD3QLYyAug/b1GW3L5fDLygIf6u1q4L9LRdiJTxEJKh7qaH5d1GfHgKKoIGN0Di/wPPYdUbP2vW3YD1oumqgLqfDghSbJ6zn7JKlKDQk1U17LckBEI5/7+hsMGDVGSg5PkPWD5SMtUbJe6NTmZ9aZg+6vMTkkxtJyet5GHak3n6I3rBxIvWjYBv9QSwECFAAUAAAACADCvvVcf7/TypwAAADkAAAAEwAAAAAAAAAAAAAAAAAAAAAAW0NvbnRlbnRfVHlwZXNdLnhtbFBLAQIUABQAAAAIAMK+9Vy5xFaLhwAAALsAAAASAAAAAAAAAAAAAAAAAM0AAABDb25maWcvUGFja2FnZS54bWxQSwECFAAUAAAACADCvvVcJbQZkRsBAAADAgAAEwAAAAAAAAAAAAAAAACEAQAARm9ybXVsYXMvU2VjdGlvbjEubVBLBQYAAAAAAwADAMIAAADQAgAAAADXAAAAPD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXRmLTgiPz48UGVybWlzc2lvbkxpc3QgeG1sbnM6eHNkPSJodHRwOi8vd3d3LnczLm9yZy8yMDAxL1hNTFNjaGVtYSI+PENhbkV2YWx1YXRlRnV0dXJlUGFja2FnZXM+ZmFsc2U8L0NhbkV2YWx1YXRlRnV0dXJlUGFja2FnZXM+PEZpcmV3YWxsRW5hYmxlZD50cnVlPC9GaXJld2FsbEVuYWJsZWQ+PC9QZXJtaXNzaW9uTGlzdD4AAAAAAAAAAA==</DataMashup>
 </file>
--- a/demo/pq-sales.xlsx
+++ b/demo/pq-sales.xlsx
@@ -125,5 +125,5 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<DataMashup xmlns="http://schemas.microsoft.com/DataMashup">AAAAAKgDAABQSwMEFAAAAAgAwr71XH+/08qcAAAA5AAAABMAAABbQ29udGVudF9UeXBlc10ueG1sbY5LDsIwDESvEnmfurBACDXtArgBF4iC+xHNR42Lwu1J6A516Zl5nmm6ZGfxpiVO3ik4VDUIcsY/JzcoWLmXZ+ja5vEJFEWOuqhgZA4XxGhGsjpWPpDLTu8Xqzmfy4BBm5ceCI91fULjHZNjyeUHtM2Ner3OLO4py1ttxkFct1ypUsCUGIuMu4D9i+sQ5sloziYmaaO0BcTf7PYLUEsDBBQAAAAIAMK+9Vy5xFaLhwAAALsAAAASAAAAQ29uZmlnL1BhY2thZ2UueG1sTY3BCgIhFEV/RdyPb2oV8XQWtR0IovZiziiNOugz+vwGSmh3D9x7Dw7vsLCXzcWnKPlO9JzZaNLDx1nySlN34IPCizZPPVu2lWOR3BGtR4BinA26iOBNTiVNJEwKcNakR11cXeE34wrvX4Paix6hAY4+tryZEf4YT3Whmq2ysbtdERpiO1UfUEsDBBQAAAAIAMK+9VwltBmRGwEAAAMCAAATAAAARm9ybXVsYXMvU2VjdGlvbjEubV2QPWvDMBCGd/+Kw5NTTCBDp5BCCe3YNrEhg/Gg2FcsIktBOrUNxv+958+YeLF00j3vc3JYkDQakuG/2QaBq4TFEj49XT3BDhRSAPwlxtsCufD2V6Ba7721qOlk7OVszCVaNdmHqHEXJkKhC/M22xtNfCOP+/b0dmXqDlJxVrhOrdDu29h6b5SvdXfooiEhhqYJD3QLYyAug/b1GW3L5fDLygIf6u1q4L9LRdiJTxEJKh7qaH5d1GfHgKKoIGN0Di/wPPYdUbP2vW3YD1oumqgLqfDghSbJ6zn7JKlKDQk1U17LckBEI5/7+hsMGDVGSg5PkPWD5SMtUbJe6NTmZ9aZg+6vMTkkxtJyet5GHak3n6I3rBxIvWjYBv9QSwECFAAUAAAACADCvvVcf7/TypwAAADkAAAAEwAAAAAAAAAAAAAAAAAAAAAAW0NvbnRlbnRfVHlwZXNdLnhtbFBLAQIUABQAAAAIAMK+9Vy5xFaLhwAAALsAAAASAAAAAAAAAAAAAAAAAM0AAABDb25maWcvUGFja2FnZS54bWxQSwECFAAUAAAACADCvvVcJbQZkRsBAAADAgAAEwAAAAAAAAAAAAAAAACEAQAARm9ybXVsYXMvU2VjdGlvbjEubVBLBQYAAAAAAwADAMIAAADQAgAAAADXAAAAPD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXRmLTgiPz48UGVybWlzc2lvbkxpc3QgeG1sbnM6eHNkPSJodHRwOi8vd3d3LnczLm9yZy8yMDAxL1hNTFNjaGVtYSI+PENhbkV2YWx1YXRlRnV0dXJlUGFja2FnZXM+ZmFsc2U8L0NhbkV2YWx1YXRlRnV0dXJlUGFja2FnZXM+PEZpcmV3YWxsRW5hYmxlZD50cnVlPC9GaXJld2FsbEVuYWJsZWQ+PC9QZXJtaXNzaW9uTGlzdD4AAAAAAAAAAA==</DataMashup>
+<DataMashup xmlns="http://schemas.microsoft.com/DataMashup">AAAAAKgDAABQSwMEFAAAAAgAeUD2XH+/08qcAAAA5AAAABMAAABbQ29udGVudF9UeXBlc10ueG1sbY5LDsIwDESvEnmfurBACDXtArgBF4iC+xHNR42Lwu1J6A516Zl5nmm6ZGfxpiVO3ik4VDUIcsY/JzcoWLmXZ+ja5vEJFEWOuqhgZA4XxGhGsjpWPpDLTu8Xqzmfy4BBm5ceCI91fULjHZNjyeUHtM2Ner3OLO4py1ttxkFct1ypUsCUGIuMu4D9i+sQ5sloziYmaaO0BcTf7PYLUEsDBBQAAAAIAHlA9ly5xFaLhwAAALsAAAASAAAAQ29uZmlnL1BhY2thZ2UueG1sTY3BCgIhFEV/RdyPb2oV8XQWtR0IovZiziiNOugz+vwGSmh3D9x7Dw7vsLCXzcWnKPlO9JzZaNLDx1nySlN34IPCizZPPVu2lWOR3BGtR4BinA26iOBNTiVNJEwKcNakR11cXeE34wrvX4Paix6hAY4+tryZEf4YT3Whmq2ysbtdERpiO1UfUEsDBBQAAAAIAHlA9lwltBmRGwEAAAMCAAATAAAARm9ybXVsYXMvU2VjdGlvbjEubV2QPWvDMBCGd/+Kw5NTTCBDp5BCCe3YNrEhg/Gg2FcsIktBOrUNxv+958+YeLF00j3vc3JYkDQakuG/2QaBq4TFEj49XT3BDhRSAPwlxtsCufD2V6Ba7721qOlk7OVszCVaNdmHqHEXJkKhC/M22xtNfCOP+/b0dmXqDlJxVrhOrdDu29h6b5SvdXfooiEhhqYJD3QLYyAug/b1GW3L5fDLygIf6u1q4L9LRdiJTxEJKh7qaH5d1GfHgKKoIGN0Di/wPPYdUbP2vW3YD1oumqgLqfDghSbJ6zn7JKlKDQk1U17LckBEI5/7+hsMGDVGSg5PkPWD5SMtUbJe6NTmZ9aZg+6vMTkkxtJyet5GHak3n6I3rBxIvWjYBv9QSwECFAAUAAAACAB5QPZcf7/TypwAAADkAAAAEwAAAAAAAAAAAAAAAAAAAAAAW0NvbnRlbnRfVHlwZXNdLnhtbFBLAQIUABQAAAAIAHlA9ly5xFaLhwAAALsAAAASAAAAAAAAAAAAAAAAAM0AAABDb25maWcvUGFja2FnZS54bWxQSwECFAAUAAAACAB5QPZcJbQZkRsBAAADAgAAEwAAAAAAAAAAAAAAAACEAQAARm9ybXVsYXMvU2VjdGlvbjEubVBLBQYAAAAAAwADAMIAAADQAgAAAADXAAAAPD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXRmLTgiPz48UGVybWlzc2lvbkxpc3QgeG1sbnM6eHNkPSJodHRwOi8vd3d3LnczLm9yZy8yMDAxL1hNTFNjaGVtYSI+PENhbkV2YWx1YXRlRnV0dXJlUGFja2FnZXM+ZmFsc2U8L0NhbkV2YWx1YXRlRnV0dXJlUGFja2FnZXM+PEZpcmV3YWxsRW5hYmxlZD50cnVlPC9GaXJld2FsbEVuYWJsZWQ+PC9QZXJtaXNzaW9uTGlzdD4AAAAAAAAAAA==</DataMashup>
 </file>